--- a/udler2018_bnmf/manifest.xlsx
+++ b/udler2018_bnmf/manifest.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="main_gwas" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="trait_gwas" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="main_gwas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="trait_gwas" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -482,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1027,6 +1027,81 @@
         <v>200000</v>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>dpa</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>/BiO2/home/daniel/udler2018_bnmf/sumstats_converted/dpa.tsv.gz</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>8866</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>palmitoleic</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>/BiO2/home/daniel/udler2018_bnmf/sumstats_converted/palmitoleic.tsv.gz</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>8961</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>n6_1821</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>/BiO2/home/daniel/udler2018_bnmf/sumstats_converted/n6_1821.tsv.gz</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>8631</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>n6_1831</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>/BiO2/home/daniel/udler2018_bnmf/sumstats_converted/n6_1831.tsv.gz</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>8631</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>n6_2031</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>/BiO2/home/daniel/udler2018_bnmf/sumstats_converted/n6_2031.tsv.gz</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>8631</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/udler2018_bnmf/manifest.xlsx
+++ b/udler2018_bnmf/manifest.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="main_gwas" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="trait_gwas" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="main_gwas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="trait_gwas" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -462,7 +462,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>./sumstats_converted/t2d_diagram_v3.tsv.gz</t>
+          <t>/BiO2/home/daniel/udler2018_bnmf/data/sumstats_converted/t2d_diagram_v3.tsv.gz</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -482,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,7 +510,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>./sumstats_converted/bl.tsv.gz</t>
+          <t>/BiO2/home/daniel/udler2018_bnmf/data/sumstats_converted/bl.tsv.gz</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -525,7 +525,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>./sumstats_converted/bmi.tsv.gz</t>
+          <t>/BiO2/home/daniel/udler2018_bnmf/data/sumstats_converted/bmi.tsv.gz</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -540,7 +540,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>./sumstats_converted/bodyfat.tsv.gz</t>
+          <t>/BiO2/home/daniel/udler2018_bnmf/data/sumstats_converted/bodyfat.tsv.gz</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -555,7 +555,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>./sumstats_converted/bw.tsv.gz</t>
+          <t>/BiO2/home/daniel/udler2018_bnmf/data/sumstats_converted/bw.tsv.gz</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -570,7 +570,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>./sumstats_converted/cir.tsv.gz</t>
+          <t>/BiO2/home/daniel/udler2018_bnmf/data/sumstats_converted/cir.tsv.gz</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -585,7 +585,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>./sumstats_converted/di.tsv.gz</t>
+          <t>/BiO2/home/daniel/udler2018_bnmf/data/sumstats_converted/di.tsv.gz</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -600,7 +600,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>./sumstats_converted/fg.tsv.gz</t>
+          <t>/BiO2/home/daniel/udler2018_bnmf/data/sumstats_converted/fg.tsv.gz</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -615,7 +615,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>./sumstats_converted/fg2hr.tsv.gz</t>
+          <t>/BiO2/home/daniel/udler2018_bnmf/data/sumstats_converted/fg2hr.tsv.gz</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -630,7 +630,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>./sumstats_converted/fi.tsv.gz</t>
+          <t>/BiO2/home/daniel/udler2018_bnmf/data/sumstats_converted/fi.tsv.gz</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -645,7 +645,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>./sumstats_converted/hba1c.tsv.gz</t>
+          <t>/BiO2/home/daniel/udler2018_bnmf/data/sumstats_converted/hba1c.tsv.gz</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -660,7 +660,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>./sumstats_converted/height.tsv.gz</t>
+          <t>/BiO2/home/daniel/udler2018_bnmf/data/sumstats_converted/height.tsv.gz</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -675,7 +675,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>./sumstats_converted/hip_f.tsv.gz</t>
+          <t>/BiO2/home/daniel/udler2018_bnmf/data/sumstats_converted/hip_f.tsv.gz</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -690,7 +690,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>./sumstats_converted/hip_m.tsv.gz</t>
+          <t>/BiO2/home/daniel/udler2018_bnmf/data/sumstats_converted/hip_m.tsv.gz</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -705,7 +705,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>./sumstats_converted/hip.tsv.gz</t>
+          <t>/BiO2/home/daniel/udler2018_bnmf/data/sumstats_converted/hip.tsv.gz</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -720,7 +720,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>./sumstats_converted/hipadjbmi.tsv.gz</t>
+          <t>/BiO2/home/daniel/udler2018_bnmf/data/sumstats_converted/hipadjbmi.tsv.gz</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -735,7 +735,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>./sumstats_converted/homab.tsv.gz</t>
+          <t>/BiO2/home/daniel/udler2018_bnmf/data/sumstats_converted/homab.tsv.gz</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -750,7 +750,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>./sumstats_converted/homair.tsv.gz</t>
+          <t>/BiO2/home/daniel/udler2018_bnmf/data/sumstats_converted/homair.tsv.gz</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -765,7 +765,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>./sumstats_converted/incr30.tsv.gz</t>
+          <t>/BiO2/home/daniel/udler2018_bnmf/data/sumstats_converted/incr30.tsv.gz</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -780,7 +780,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>./sumstats_converted/ins30_bmi.tsv.gz</t>
+          <t>/BiO2/home/daniel/udler2018_bnmf/data/sumstats_converted/ins30_bmi.tsv.gz</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -795,7 +795,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>./sumstats_converted/isi.tsv.gz</t>
+          <t>/BiO2/home/daniel/udler2018_bnmf/data/sumstats_converted/isi.tsv.gz</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -810,7 +810,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>./sumstats_converted/isibmi.tsv.gz</t>
+          <t>/BiO2/home/daniel/udler2018_bnmf/data/sumstats_converted/isibmi.tsv.gz</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -825,7 +825,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>./sumstats_converted/leptin.tsv.gz</t>
+          <t>/BiO2/home/daniel/udler2018_bnmf/data/sumstats_converted/leptin.tsv.gz</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>./sumstats_converted/proins.tsv.gz</t>
+          <t>/BiO2/home/daniel/udler2018_bnmf/data/sumstats_converted/proins.tsv.gz</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -855,7 +855,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>./sumstats_converted/sat.tsv.gz</t>
+          <t>/BiO2/home/daniel/udler2018_bnmf/data/sumstats_converted/sat.tsv.gz</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -870,7 +870,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>./sumstats_converted/urate.tsv.gz</t>
+          <t>/BiO2/home/daniel/udler2018_bnmf/data/sumstats_converted/urate.tsv.gz</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -885,7 +885,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>./sumstats_converted/vat_adjbmi.tsv.gz</t>
+          <t>/BiO2/home/daniel/udler2018_bnmf/data/sumstats_converted/vat_adjbmi.tsv.gz</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -900,7 +900,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>./sumstats_converted/vat.tsv.gz</t>
+          <t>/BiO2/home/daniel/udler2018_bnmf/data/sumstats_converted/vat.tsv.gz</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -915,7 +915,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>./sumstats_converted/wc_female.tsv.gz</t>
+          <t>/BiO2/home/daniel/udler2018_bnmf/data/sumstats_converted/wc_female.tsv.gz</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -930,7 +930,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>./sumstats_converted/wc_male.tsv.gz</t>
+          <t>/BiO2/home/daniel/udler2018_bnmf/data/sumstats_converted/wc_male.tsv.gz</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -945,7 +945,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>./sumstats_converted/wc.tsv.gz</t>
+          <t>/BiO2/home/daniel/udler2018_bnmf/data/sumstats_converted/wc.tsv.gz</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -960,7 +960,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>./sumstats_converted/wcadjbmi.tsv.gz</t>
+          <t>/BiO2/home/daniel/udler2018_bnmf/data/sumstats_converted/wcadjbmi.tsv.gz</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -975,7 +975,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>./sumstats_converted/whr_f.tsv.gz</t>
+          <t>/BiO2/home/daniel/udler2018_bnmf/data/sumstats_converted/whr_f.tsv.gz</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -990,7 +990,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>./sumstats_converted/whr_m.tsv.gz</t>
+          <t>/BiO2/home/daniel/udler2018_bnmf/data/sumstats_converted/whr_m.tsv.gz</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>./sumstats_converted/whr.tsv.gz</t>
+          <t>/BiO2/home/daniel/udler2018_bnmf/data/sumstats_converted/whr.tsv.gz</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -1020,11 +1020,146 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>./sumstats_converted/whradjbmi.tsv.gz</t>
+          <t>/BiO2/home/daniel/udler2018_bnmf/data/sumstats_converted/whradjbmi.tsv.gz</t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>200000</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>dpa</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>/BiO2/home/daniel/udler2018_bnmf/data/sumstats_converted/dpa.tsv.gz</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>8866</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>palmitoleic</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>/BiO2/home/daniel/udler2018_bnmf/data/sumstats_converted/palmitoleic.tsv.gz</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>8961</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>n6_1821</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>/BiO2/home/daniel/udler2018_bnmf/data/sumstats_converted/n6_1821.tsv.gz</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>8631</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>n6_1831</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>/BiO2/home/daniel/udler2018_bnmf/data/sumstats_converted/n6_1831.tsv.gz</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>8631</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>n6_2031</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>/BiO2/home/daniel/udler2018_bnmf/data/sumstats_converted/n6_2031.tsv.gz</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>8631</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>hdl</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>/BiO2/home/daniel/udler2018_bnmf/data/sumstats_converted/hdl.tsv.gz</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>94302</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ldl</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>/BiO2/home/daniel/udler2018_bnmf/data/sumstats_converted/ldl.tsv.gz</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>89880</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>/BiO2/home/daniel/udler2018_bnmf/data/sumstats_converted/tc.tsv.gz</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>94586</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>tg</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>/BiO2/home/daniel/udler2018_bnmf/data/sumstats_converted/tg.tsv.gz</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>91004</v>
       </c>
     </row>
   </sheetData>
